--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2636-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2636-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{350B5A22-684E-4DFA-8F29-1BE842F71D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E35BF7D-8C6A-470E-8BDC-B572225DFC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{367A790E-CED8-4B0C-9BDA-D09FE6FAF9BE}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{82ABE044-388C-45F4-91BA-ADE5EE137712}"/>
   </bookViews>
   <sheets>
     <sheet name="2636-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1466,25 +1466,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D69A910-F888-4DDA-9669-270F8F7C5B27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{145F9256-0B42-4762-BE35-7AFBDBA8FCAF}">
   <dimension ref="A1:R31"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1512,7 +1512,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1542,7 +1542,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1638,7 +1638,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>6.54</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2022</v>
       </c>
@@ -2246,7 +2246,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2021</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="39">
         <v>2020</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2019</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>8.2899999999999991</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2018</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2017</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2016</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>8.44</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2015</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2014</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2013</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2012</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2011</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2010</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <v>2009</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2008</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2007</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39" t="s">
         <v>41</v>
       </c>
